--- a/RETUNE_recruitment.xlsx
+++ b/RETUNE_recruitment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usbch.sharepoint.com/teams/c0620/Freigegebene Dokumente/RETUNE/18_website/RETUNE_website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1738" documentId="8_{51399C67-AD59-964E-9247-4C3D428189F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24A6116F-34C8-9C47-843C-D336776C3EE4}"/>
+  <xr:revisionPtr revIDLastSave="1817" documentId="8_{51399C67-AD59-964E-9247-4C3D428189F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCEC185A-9CFB-6E49-8493-64C6323E4F7D}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="18960" xr2:uid="{1D389274-2DC7-8A41-9A7B-CCBF56013A3F}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{1D389274-2DC7-8A41-9A7B-CCBF56013A3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="15">
   <si>
     <t>Date</t>
   </si>
@@ -78,6 +78,9 @@
   </si>
   <si>
     <t>St. Gallen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zurich </t>
   </si>
 </sst>
 </file>
@@ -490,7 +493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDFC9B8A-85DD-B049-AB11-35BA14E37F74}">
-  <dimension ref="A1:G716"/>
+  <dimension ref="A1:G762"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
@@ -8863,6 +8866,592 @@
         <v>46170</v>
       </c>
       <c r="E716">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="717" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A717" s="7">
+        <v>46232</v>
+      </c>
+      <c r="B717" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C717">
+        <v>1</v>
+      </c>
+      <c r="D717" s="8">
+        <v>1</v>
+      </c>
+      <c r="E717" s="8"/>
+      <c r="F717" s="8"/>
+    </row>
+    <row r="718" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A718" s="7">
+        <v>46230</v>
+      </c>
+      <c r="B718" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C718">
+        <v>1</v>
+      </c>
+      <c r="D718" s="8">
+        <v>0</v>
+      </c>
+      <c r="E718" s="8"/>
+      <c r="F718" s="8"/>
+    </row>
+    <row r="719" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A719" s="7">
+        <v>46223</v>
+      </c>
+      <c r="B719" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C719">
+        <v>1</v>
+      </c>
+      <c r="D719" s="8">
+        <v>0</v>
+      </c>
+      <c r="E719" s="8"/>
+    </row>
+    <row r="720" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A720" s="7">
+        <v>46220</v>
+      </c>
+      <c r="B720" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C720">
+        <v>1</v>
+      </c>
+      <c r="D720" s="8">
+        <v>1</v>
+      </c>
+      <c r="E720" s="8"/>
+      <c r="F720" s="8"/>
+    </row>
+    <row r="721" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A721" s="7">
+        <v>46216</v>
+      </c>
+      <c r="B721" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C721">
+        <v>1</v>
+      </c>
+      <c r="D721" s="8">
+        <v>0</v>
+      </c>
+      <c r="E721" s="8"/>
+      <c r="F721" s="8"/>
+    </row>
+    <row r="722" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A722" s="7">
+        <v>46216</v>
+      </c>
+      <c r="B722" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C722">
+        <v>1</v>
+      </c>
+      <c r="D722" s="8">
+        <v>0</v>
+      </c>
+      <c r="E722" s="8"/>
+      <c r="F722" s="8"/>
+    </row>
+    <row r="723" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A723" s="7">
+        <v>46211</v>
+      </c>
+      <c r="B723" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C723">
+        <v>1</v>
+      </c>
+      <c r="D723" s="8">
+        <v>0</v>
+      </c>
+      <c r="E723" s="8"/>
+      <c r="F723" s="8"/>
+    </row>
+    <row r="724" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A724" s="7">
+        <v>46210</v>
+      </c>
+      <c r="B724" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C724">
+        <v>1</v>
+      </c>
+      <c r="D724" s="8">
+        <v>0</v>
+      </c>
+      <c r="E724" s="8"/>
+      <c r="F724" s="8"/>
+    </row>
+    <row r="725" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A725" s="7">
+        <v>46205</v>
+      </c>
+      <c r="B725" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C725">
+        <v>1</v>
+      </c>
+      <c r="D725" s="8">
+        <v>0</v>
+      </c>
+      <c r="E725" s="8"/>
+      <c r="F725" s="8"/>
+    </row>
+    <row r="726" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A726" s="7">
+        <v>46204</v>
+      </c>
+      <c r="B726" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C726">
+        <v>1</v>
+      </c>
+      <c r="D726" s="8">
+        <v>0</v>
+      </c>
+      <c r="E726" s="8"/>
+      <c r="F726" s="8"/>
+    </row>
+    <row r="727" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A727" s="7">
+        <v>46199</v>
+      </c>
+      <c r="B727" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C727">
+        <v>1</v>
+      </c>
+      <c r="D727" s="8">
+        <v>0</v>
+      </c>
+      <c r="E727" s="8"/>
+      <c r="F727" s="8"/>
+    </row>
+    <row r="728" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A728" s="7">
+        <v>46197</v>
+      </c>
+      <c r="B728" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C728">
+        <v>1</v>
+      </c>
+      <c r="D728" s="8">
+        <v>0</v>
+      </c>
+      <c r="E728" s="8"/>
+      <c r="F728" s="8"/>
+    </row>
+    <row r="729" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A729" s="7">
+        <v>46195</v>
+      </c>
+      <c r="B729" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C729">
+        <v>1</v>
+      </c>
+      <c r="D729" s="8">
+        <v>1</v>
+      </c>
+      <c r="E729" s="8"/>
+      <c r="F729" s="8"/>
+    </row>
+    <row r="730" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A730" s="7">
+        <v>46190</v>
+      </c>
+      <c r="B730" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C730">
+        <v>1</v>
+      </c>
+      <c r="D730" s="8">
+        <v>1</v>
+      </c>
+      <c r="E730" s="8"/>
+      <c r="F730" s="8"/>
+    </row>
+    <row r="731" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A731" s="7">
+        <v>46189</v>
+      </c>
+      <c r="B731" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C731">
+        <v>1</v>
+      </c>
+      <c r="D731" s="8">
+        <v>1</v>
+      </c>
+      <c r="E731" s="8"/>
+      <c r="F731" s="8"/>
+    </row>
+    <row r="732" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A732" s="7">
+        <v>46189</v>
+      </c>
+      <c r="B732" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C732">
+        <v>1</v>
+      </c>
+      <c r="D732" s="8">
+        <v>0</v>
+      </c>
+      <c r="E732" s="8"/>
+      <c r="F732" s="8"/>
+    </row>
+    <row r="733" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A733" s="7">
+        <v>46189</v>
+      </c>
+      <c r="B733" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C733">
+        <v>1</v>
+      </c>
+      <c r="D733" s="8">
+        <v>1</v>
+      </c>
+      <c r="E733" s="8"/>
+      <c r="F733" s="8"/>
+    </row>
+    <row r="734" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A734" s="7">
+        <v>46185</v>
+      </c>
+      <c r="B734" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C734">
+        <v>1</v>
+      </c>
+      <c r="D734" s="8">
+        <v>1</v>
+      </c>
+      <c r="E734" s="8"/>
+      <c r="F734" s="8"/>
+    </row>
+    <row r="735" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A735" s="7">
+        <v>46185</v>
+      </c>
+      <c r="B735" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C735">
+        <v>1</v>
+      </c>
+      <c r="D735" s="8">
+        <v>0</v>
+      </c>
+      <c r="E735" s="8"/>
+      <c r="F735" s="8"/>
+    </row>
+    <row r="736" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A736" s="7">
+        <v>46185</v>
+      </c>
+      <c r="B736" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C736">
+        <v>1</v>
+      </c>
+      <c r="D736" s="8">
+        <v>1</v>
+      </c>
+      <c r="E736" s="8"/>
+      <c r="F736" s="8"/>
+    </row>
+    <row r="737" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A737" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B737" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C737">
+        <v>1</v>
+      </c>
+      <c r="D737" s="8">
+        <v>1</v>
+      </c>
+      <c r="E737" s="8"/>
+      <c r="F737" s="8"/>
+    </row>
+    <row r="738" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A738" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B738" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C738">
+        <v>1</v>
+      </c>
+      <c r="D738" s="8">
+        <v>0</v>
+      </c>
+      <c r="E738" s="8"/>
+      <c r="F738" s="8"/>
+    </row>
+    <row r="739" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A739" s="7">
+        <v>46182</v>
+      </c>
+      <c r="B739" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C739">
+        <v>1</v>
+      </c>
+      <c r="D739" s="8">
+        <v>0</v>
+      </c>
+      <c r="E739" s="8"/>
+      <c r="F739" s="8"/>
+    </row>
+    <row r="740" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A740" s="10">
+        <v>46175</v>
+      </c>
+      <c r="B740" s="8"/>
+      <c r="C740" s="8"/>
+      <c r="D740" s="8"/>
+      <c r="E740" s="8">
+        <v>1</v>
+      </c>
+      <c r="F740" s="8"/>
+      <c r="G740" s="8"/>
+    </row>
+    <row r="741" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A741" s="10">
+        <v>46204</v>
+      </c>
+      <c r="B741" s="8"/>
+      <c r="C741" s="8"/>
+      <c r="D741" s="8"/>
+      <c r="E741" s="8">
+        <v>1</v>
+      </c>
+      <c r="F741" s="8"/>
+      <c r="G741" s="8"/>
+    </row>
+    <row r="742" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A742" s="10">
+        <v>46227</v>
+      </c>
+      <c r="B742" s="8"/>
+      <c r="C742" s="8"/>
+      <c r="D742" s="8"/>
+      <c r="E742" s="8">
+        <v>1</v>
+      </c>
+      <c r="F742" s="8"/>
+      <c r="G742" s="8"/>
+    </row>
+    <row r="743" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A743" s="10">
+        <v>46219</v>
+      </c>
+      <c r="B743" s="8"/>
+      <c r="C743" s="8"/>
+      <c r="D743" s="8"/>
+      <c r="E743" s="8">
+        <v>1</v>
+      </c>
+      <c r="F743" s="8"/>
+      <c r="G743" s="8"/>
+    </row>
+    <row r="744" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A744" s="10">
+        <v>46190</v>
+      </c>
+      <c r="B744" s="8"/>
+      <c r="C744" s="8"/>
+      <c r="D744" s="8"/>
+      <c r="E744" s="8">
+        <v>1</v>
+      </c>
+      <c r="F744" s="8"/>
+      <c r="G744" s="8"/>
+    </row>
+    <row r="745" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A745" s="10">
+        <v>46227</v>
+      </c>
+      <c r="B745" s="8"/>
+      <c r="C745" s="8"/>
+      <c r="D745" s="8"/>
+      <c r="E745" s="8">
+        <v>1</v>
+      </c>
+      <c r="F745" s="8"/>
+      <c r="G745" s="8"/>
+    </row>
+    <row r="746" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A746" s="10">
+        <v>46218</v>
+      </c>
+      <c r="B746" s="8"/>
+      <c r="C746" s="8"/>
+      <c r="D746" s="8"/>
+      <c r="E746" s="8">
+        <v>1</v>
+      </c>
+      <c r="F746" s="8"/>
+      <c r="G746" s="8"/>
+    </row>
+    <row r="747" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A747" s="10">
+        <v>46198</v>
+      </c>
+      <c r="E747" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="748" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A748" s="10">
+        <v>46182</v>
+      </c>
+      <c r="E748" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="749" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A749" s="10">
+        <v>46217</v>
+      </c>
+      <c r="E749" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="750" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A750" s="10">
+        <v>46212</v>
+      </c>
+      <c r="E750">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="751" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A751" s="10">
+        <v>46196</v>
+      </c>
+      <c r="E751">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="752" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A752" s="10">
+        <v>46211</v>
+      </c>
+      <c r="E752">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="753" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A753" s="10">
+        <v>46190</v>
+      </c>
+      <c r="E753">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="754" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A754" s="10">
+        <v>46232</v>
+      </c>
+      <c r="E754">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="755" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A755" s="10">
+        <v>46205</v>
+      </c>
+      <c r="E755">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="756" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A756" s="10">
+        <v>46227</v>
+      </c>
+      <c r="E756">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="757" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A757" s="10">
+        <v>46219</v>
+      </c>
+      <c r="E757">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="758" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A758" s="10">
+        <v>46204</v>
+      </c>
+      <c r="E758">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="759" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A759" s="10">
+        <v>46202</v>
+      </c>
+      <c r="E759">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="760" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A760" s="10">
+        <v>46213</v>
+      </c>
+      <c r="E760">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="761" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A761" s="10">
+        <v>46230</v>
+      </c>
+      <c r="E761">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="762" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A762" s="10">
+        <v>46227</v>
+      </c>
+      <c r="E762">
         <v>1</v>
       </c>
     </row>
@@ -8875,28 +9464,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Confidentiality xmlns="ee2de805-d424-449f-84ad-9da0e2dd7d39">Intern</Confidentiality>
-    <Patientdata xmlns="ee2de805-d424-449f-84ad-9da0e2dd7d39">false</Patientdata>
-    <TaxCatchAll xmlns="ee2de805-d424-449f-84ad-9da0e2dd7d39" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4c57b41f-cbf4-457f-bf80-bd53c8e26310">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="USB-Dokument" ma:contentTypeID="0x01010074254FFFFA788748BE9570FD90FA56DE00A6BA077A5C2D0748B0D413E1B37C0DF4" ma:contentTypeVersion="19" ma:contentTypeDescription="Ein neues USB-Dokument in der Bibliothek erstellen." ma:contentTypeScope="" ma:versionID="c510736d7b8df5493d0c0cbf1b659039">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ee2de805-d424-449f-84ad-9da0e2dd7d39" xmlns:ns3="4c57b41f-cbf4-457f-bf80-bd53c8e26310" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="30d006a702a85f058c7f942dd83db01e" ns2:_="" ns3:_="">
     <xsd:import namespace="ee2de805-d424-449f-84ad-9da0e2dd7d39"/>
@@ -9113,32 +9680,29 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0DBF876-E745-42DF-BD17-181B14022097}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Confidentiality xmlns="ee2de805-d424-449f-84ad-9da0e2dd7d39">Intern</Confidentiality>
+    <Patientdata xmlns="ee2de805-d424-449f-84ad-9da0e2dd7d39">false</Patientdata>
+    <TaxCatchAll xmlns="ee2de805-d424-449f-84ad-9da0e2dd7d39" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4c57b41f-cbf4-457f-bf80-bd53c8e26310">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF03F65C-5CED-4A89-8A63-D9B2AEB56D23}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="4c57b41f-cbf4-457f-bf80-bd53c8e26310"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="ee2de805-d424-449f-84ad-9da0e2dd7d39"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53E67CF1-8A7B-44D0-A2A1-F624F69C8C2A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9155,4 +9719,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF03F65C-5CED-4A89-8A63-D9B2AEB56D23}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="4c57b41f-cbf4-457f-bf80-bd53c8e26310"/>
+    <ds:schemaRef ds:uri="ee2de805-d424-449f-84ad-9da0e2dd7d39"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0DBF876-E745-42DF-BD17-181B14022097}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/RETUNE_recruitment.xlsx
+++ b/RETUNE_recruitment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usbch.sharepoint.com/teams/c0620/Freigegebene Dokumente/RETUNE/18_website/RETUNE_website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1817" documentId="8_{51399C67-AD59-964E-9247-4C3D428189F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCEC185A-9CFB-6E49-8493-64C6323E4F7D}"/>
+  <xr:revisionPtr revIDLastSave="1869" documentId="8_{51399C67-AD59-964E-9247-4C3D428189F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D97DED78-E65C-8047-BF17-653B029280FF}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{1D389274-2DC7-8A41-9A7B-CCBF56013A3F}"/>
+    <workbookView xWindow="9940" yWindow="5320" windowWidth="30240" windowHeight="17040" xr2:uid="{1D389274-2DC7-8A41-9A7B-CCBF56013A3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="15">
   <si>
     <t>Date</t>
   </si>
@@ -493,7 +493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDFC9B8A-85DD-B049-AB11-35BA14E37F74}">
-  <dimension ref="A1:G762"/>
+  <dimension ref="A1:G792"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
@@ -9375,7 +9375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="753" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A753" s="10">
         <v>46190</v>
       </c>
@@ -9383,7 +9383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="754" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A754" s="10">
         <v>46232</v>
       </c>
@@ -9391,7 +9391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="755" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A755" s="10">
         <v>46205</v>
       </c>
@@ -9399,7 +9399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="756" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A756" s="10">
         <v>46227</v>
       </c>
@@ -9407,7 +9407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="757" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A757" s="10">
         <v>46219</v>
       </c>
@@ -9415,7 +9415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="758" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A758" s="10">
         <v>46204</v>
       </c>
@@ -9423,7 +9423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="759" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A759" s="10">
         <v>46202</v>
       </c>
@@ -9431,7 +9431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="760" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A760" s="10">
         <v>46213</v>
       </c>
@@ -9439,7 +9439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="761" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A761" s="10">
         <v>46230</v>
       </c>
@@ -9447,11 +9447,371 @@
         <v>1</v>
       </c>
     </row>
-    <row r="762" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A762" s="10">
         <v>46227</v>
       </c>
       <c r="E762">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="763" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A763" s="7">
+        <v>46268</v>
+      </c>
+      <c r="B763" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C763">
+        <v>1</v>
+      </c>
+      <c r="D763" s="8">
+        <v>1</v>
+      </c>
+      <c r="E763" s="8"/>
+      <c r="F763" s="8"/>
+    </row>
+    <row r="764" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A764" s="7">
+        <v>46262</v>
+      </c>
+      <c r="B764" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C764">
+        <v>1</v>
+      </c>
+      <c r="D764" s="8">
+        <v>1</v>
+      </c>
+      <c r="E764" s="8"/>
+      <c r="F764" s="8"/>
+    </row>
+    <row r="765" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A765" s="7">
+        <v>46262</v>
+      </c>
+      <c r="B765" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C765">
+        <v>1</v>
+      </c>
+      <c r="D765" s="8">
+        <v>1</v>
+      </c>
+      <c r="E765" s="8"/>
+      <c r="F765" s="8"/>
+    </row>
+    <row r="766" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A766" s="7">
+        <v>46261</v>
+      </c>
+      <c r="B766" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C766">
+        <v>1</v>
+      </c>
+      <c r="D766" s="8">
+        <v>0</v>
+      </c>
+      <c r="E766" s="8"/>
+      <c r="F766" s="8"/>
+    </row>
+    <row r="767" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A767" s="7">
+        <v>46261</v>
+      </c>
+      <c r="B767" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C767">
+        <v>1</v>
+      </c>
+      <c r="D767" s="8">
+        <v>0</v>
+      </c>
+      <c r="E767" s="8"/>
+      <c r="F767" s="8"/>
+    </row>
+    <row r="768" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A768" s="7">
+        <v>46258</v>
+      </c>
+      <c r="B768" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C768">
+        <v>1</v>
+      </c>
+      <c r="D768" s="8">
+        <v>0</v>
+      </c>
+      <c r="E768" s="8"/>
+      <c r="F768" s="8"/>
+    </row>
+    <row r="769" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A769" s="7">
+        <v>46255</v>
+      </c>
+      <c r="B769" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C769">
+        <v>1</v>
+      </c>
+      <c r="D769" s="8">
+        <v>0</v>
+      </c>
+      <c r="E769" s="8"/>
+      <c r="F769" s="8"/>
+    </row>
+    <row r="770" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A770" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B770" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C770">
+        <v>1</v>
+      </c>
+      <c r="D770" s="8">
+        <v>1</v>
+      </c>
+      <c r="E770" s="8"/>
+      <c r="F770" s="8"/>
+    </row>
+    <row r="771" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A771" s="7">
+        <v>46253</v>
+      </c>
+      <c r="B771" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C771">
+        <v>1</v>
+      </c>
+      <c r="D771" s="8">
+        <v>1</v>
+      </c>
+      <c r="E771" s="8"/>
+      <c r="F771" s="8"/>
+    </row>
+    <row r="772" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A772" s="7">
+        <v>46175</v>
+      </c>
+      <c r="B772" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C772">
+        <v>1</v>
+      </c>
+      <c r="D772" s="8">
+        <v>0</v>
+      </c>
+      <c r="E772" s="8"/>
+      <c r="F772" s="8"/>
+    </row>
+    <row r="773" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A773" s="7">
+        <v>46253</v>
+      </c>
+      <c r="B773" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C773">
+        <v>1</v>
+      </c>
+      <c r="D773" s="8">
+        <v>1</v>
+      </c>
+      <c r="E773" s="8"/>
+      <c r="F773" s="8"/>
+    </row>
+    <row r="774" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A774" s="7">
+        <v>46247</v>
+      </c>
+      <c r="B774" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C774">
+        <v>1</v>
+      </c>
+      <c r="D774" s="8">
+        <v>0</v>
+      </c>
+      <c r="E774" s="8"/>
+      <c r="F774" s="8"/>
+    </row>
+    <row r="775" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A775" s="7">
+        <v>46240</v>
+      </c>
+      <c r="B775" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C775">
+        <v>1</v>
+      </c>
+      <c r="D775" s="8">
+        <v>0</v>
+      </c>
+      <c r="E775" s="8"/>
+      <c r="F775" s="8"/>
+    </row>
+    <row r="776" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A776" s="7">
+        <v>46238</v>
+      </c>
+      <c r="B776" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C776">
+        <v>1</v>
+      </c>
+      <c r="D776" s="8">
+        <v>1</v>
+      </c>
+      <c r="E776" s="8"/>
+      <c r="F776" s="8"/>
+    </row>
+    <row r="777" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A777" s="7">
+        <v>46237</v>
+      </c>
+      <c r="B777" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C777">
+        <v>1</v>
+      </c>
+      <c r="D777" s="8">
+        <v>0</v>
+      </c>
+      <c r="E777" s="8"/>
+      <c r="F777" s="8"/>
+    </row>
+    <row r="778" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A778" s="10">
+        <v>46248</v>
+      </c>
+      <c r="E778">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="779" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A779" s="10">
+        <v>46240</v>
+      </c>
+      <c r="E779">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="780" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A780" s="10">
+        <v>46267</v>
+      </c>
+      <c r="E780">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="781" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A781" s="10">
+        <v>46239</v>
+      </c>
+      <c r="E781">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="782" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A782" s="10">
+        <v>46246</v>
+      </c>
+      <c r="E782">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="783" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A783" s="10">
+        <v>46254</v>
+      </c>
+      <c r="E783">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="784" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A784" s="10">
+        <v>46246</v>
+      </c>
+      <c r="E784">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="785" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A785" s="10">
+        <v>46245</v>
+      </c>
+      <c r="E785">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="786" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A786" s="10">
+        <v>46267</v>
+      </c>
+      <c r="E786">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="787" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A787" s="10">
+        <v>46253</v>
+      </c>
+      <c r="E787">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="788" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A788" s="10">
+        <v>46265</v>
+      </c>
+      <c r="E788">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="789" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A789" s="10">
+        <v>46253</v>
+      </c>
+      <c r="E789">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="790" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A790" s="10">
+        <v>46240</v>
+      </c>
+      <c r="E790">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="791" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A791" s="10">
+        <v>46255</v>
+      </c>
+      <c r="E791">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="792" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A792" s="10">
+        <v>46254</v>
+      </c>
+      <c r="E792">
         <v>1</v>
       </c>
     </row>
@@ -9464,6 +9824,28 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Confidentiality xmlns="ee2de805-d424-449f-84ad-9da0e2dd7d39">Intern</Confidentiality>
+    <Patientdata xmlns="ee2de805-d424-449f-84ad-9da0e2dd7d39">false</Patientdata>
+    <TaxCatchAll xmlns="ee2de805-d424-449f-84ad-9da0e2dd7d39" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4c57b41f-cbf4-457f-bf80-bd53c8e26310">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="USB-Dokument" ma:contentTypeID="0x01010074254FFFFA788748BE9570FD90FA56DE00A6BA077A5C2D0748B0D413E1B37C0DF4" ma:contentTypeVersion="19" ma:contentTypeDescription="Ein neues USB-Dokument in der Bibliothek erstellen." ma:contentTypeScope="" ma:versionID="c510736d7b8df5493d0c0cbf1b659039">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ee2de805-d424-449f-84ad-9da0e2dd7d39" xmlns:ns3="4c57b41f-cbf4-457f-bf80-bd53c8e26310" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="30d006a702a85f058c7f942dd83db01e" ns2:_="" ns3:_="">
     <xsd:import namespace="ee2de805-d424-449f-84ad-9da0e2dd7d39"/>
@@ -9680,29 +10062,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Confidentiality xmlns="ee2de805-d424-449f-84ad-9da0e2dd7d39">Intern</Confidentiality>
-    <Patientdata xmlns="ee2de805-d424-449f-84ad-9da0e2dd7d39">false</Patientdata>
-    <TaxCatchAll xmlns="ee2de805-d424-449f-84ad-9da0e2dd7d39" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4c57b41f-cbf4-457f-bf80-bd53c8e26310">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0DBF876-E745-42DF-BD17-181B14022097}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF03F65C-5CED-4A89-8A63-D9B2AEB56D23}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="4c57b41f-cbf4-457f-bf80-bd53c8e26310"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="ee2de805-d424-449f-84ad-9da0e2dd7d39"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53E67CF1-8A7B-44D0-A2A1-F624F69C8C2A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9719,29 +10104,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF03F65C-5CED-4A89-8A63-D9B2AEB56D23}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="4c57b41f-cbf4-457f-bf80-bd53c8e26310"/>
-    <ds:schemaRef ds:uri="ee2de805-d424-449f-84ad-9da0e2dd7d39"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0DBF876-E745-42DF-BD17-181B14022097}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/RETUNE_recruitment.xlsx
+++ b/RETUNE_recruitment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usbch.sharepoint.com/teams/c0620/Freigegebene Dokumente/RETUNE/18_website/RETUNE_website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1869" documentId="8_{51399C67-AD59-964E-9247-4C3D428189F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D97DED78-E65C-8047-BF17-653B029280FF}"/>
+  <xr:revisionPtr revIDLastSave="1927" documentId="8_{51399C67-AD59-964E-9247-4C3D428189F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{722F7C85-A03E-AB4A-87C5-8374EABA5660}"/>
   <bookViews>
-    <workbookView xWindow="9940" yWindow="5320" windowWidth="30240" windowHeight="17040" xr2:uid="{1D389274-2DC7-8A41-9A7B-CCBF56013A3F}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17040" xr2:uid="{1D389274-2DC7-8A41-9A7B-CCBF56013A3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="15">
   <si>
     <t>Date</t>
   </si>
@@ -493,7 +493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDFC9B8A-85DD-B049-AB11-35BA14E37F74}">
-  <dimension ref="A1:G792"/>
+  <dimension ref="A1:G820"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
@@ -9751,7 +9751,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="785" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="785" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A785" s="10">
         <v>46245</v>
       </c>
@@ -9759,7 +9759,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="786" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="786" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A786" s="10">
         <v>46267</v>
       </c>
@@ -9767,7 +9767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="787" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="787" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A787" s="10">
         <v>46253</v>
       </c>
@@ -9775,7 +9775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="788" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="788" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A788" s="10">
         <v>46265</v>
       </c>
@@ -9783,7 +9783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="789" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="789" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A789" s="10">
         <v>46253</v>
       </c>
@@ -9791,7 +9791,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="790" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="790" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A790" s="10">
         <v>46240</v>
       </c>
@@ -9799,7 +9799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="791" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="791" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A791" s="10">
         <v>46255</v>
       </c>
@@ -9807,11 +9807,345 @@
         <v>1</v>
       </c>
     </row>
-    <row r="792" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="792" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A792" s="10">
         <v>46254</v>
       </c>
       <c r="E792">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="793" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A793" s="7">
+        <v>46303</v>
+      </c>
+      <c r="B793" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C793" s="8">
+        <v>1</v>
+      </c>
+      <c r="D793" s="8">
+        <v>0</v>
+      </c>
+      <c r="F793" s="8"/>
+      <c r="G793" s="8"/>
+    </row>
+    <row r="794" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A794" s="7">
+        <v>46297</v>
+      </c>
+      <c r="B794" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C794" s="8">
+        <v>1</v>
+      </c>
+      <c r="D794" s="8">
+        <v>1</v>
+      </c>
+      <c r="F794" s="8"/>
+      <c r="G794" s="8"/>
+    </row>
+    <row r="795" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A795" s="7">
+        <v>46295</v>
+      </c>
+      <c r="B795" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C795" s="8">
+        <v>1</v>
+      </c>
+      <c r="D795" s="8">
+        <v>1</v>
+      </c>
+      <c r="F795" s="8"/>
+      <c r="G795" s="8"/>
+    </row>
+    <row r="796" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A796" s="7">
+        <v>46295</v>
+      </c>
+      <c r="B796" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C796" s="8">
+        <v>1</v>
+      </c>
+      <c r="D796" s="8">
+        <v>1</v>
+      </c>
+      <c r="F796" s="8"/>
+      <c r="G796" s="8"/>
+    </row>
+    <row r="797" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A797" s="7">
+        <v>46293</v>
+      </c>
+      <c r="B797" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C797" s="8">
+        <v>1</v>
+      </c>
+      <c r="D797" s="8">
+        <v>1</v>
+      </c>
+      <c r="F797" s="8"/>
+      <c r="G797" s="8"/>
+    </row>
+    <row r="798" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A798" s="7">
+        <v>46290</v>
+      </c>
+      <c r="B798" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C798" s="8">
+        <v>1</v>
+      </c>
+      <c r="D798" s="8">
+        <v>0</v>
+      </c>
+      <c r="F798" s="8"/>
+      <c r="G798" s="8"/>
+    </row>
+    <row r="799" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A799" s="7">
+        <v>46288</v>
+      </c>
+      <c r="B799" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C799" s="8">
+        <v>1</v>
+      </c>
+      <c r="D799" s="8">
+        <v>0</v>
+      </c>
+      <c r="F799" s="8"/>
+      <c r="G799" s="8"/>
+    </row>
+    <row r="800" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A800" s="7">
+        <v>46287</v>
+      </c>
+      <c r="B800" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C800" s="8">
+        <v>1</v>
+      </c>
+      <c r="D800" s="8">
+        <v>0</v>
+      </c>
+      <c r="F800" s="8"/>
+      <c r="G800" s="8"/>
+    </row>
+    <row r="801" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A801" s="7">
+        <v>46286</v>
+      </c>
+      <c r="B801" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C801" s="8">
+        <v>1</v>
+      </c>
+      <c r="D801" s="8">
+        <v>0</v>
+      </c>
+      <c r="F801" s="8"/>
+      <c r="G801" s="8"/>
+    </row>
+    <row r="802" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A802" s="7">
+        <v>46286</v>
+      </c>
+      <c r="B802" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C802" s="8">
+        <v>1</v>
+      </c>
+      <c r="D802" s="8">
+        <v>1</v>
+      </c>
+      <c r="F802" s="8"/>
+      <c r="G802" s="8"/>
+    </row>
+    <row r="803" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A803" s="7">
+        <v>46286</v>
+      </c>
+      <c r="B803" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C803" s="8">
+        <v>1</v>
+      </c>
+      <c r="D803" s="8">
+        <v>0</v>
+      </c>
+      <c r="F803" s="8"/>
+      <c r="G803" s="8"/>
+    </row>
+    <row r="804" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A804" s="7">
+        <v>46128</v>
+      </c>
+      <c r="B804" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C804" s="8">
+        <v>1</v>
+      </c>
+      <c r="D804" s="8">
+        <v>0</v>
+      </c>
+      <c r="F804" s="8"/>
+      <c r="G804" s="8"/>
+    </row>
+    <row r="805" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A805" s="7">
+        <v>46272</v>
+      </c>
+      <c r="B805" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C805" s="8">
+        <v>1</v>
+      </c>
+      <c r="D805" s="8">
+        <v>0</v>
+      </c>
+      <c r="F805" s="8"/>
+      <c r="G805" s="8"/>
+    </row>
+    <row r="806" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A806" s="1">
+        <v>46272</v>
+      </c>
+      <c r="B806" t="s">
+        <v>9</v>
+      </c>
+      <c r="C806" s="8">
+        <v>1</v>
+      </c>
+      <c r="D806">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="807" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A807" s="10">
+        <v>46274</v>
+      </c>
+      <c r="E807">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="808" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A808" s="10">
+        <v>46286</v>
+      </c>
+      <c r="E808">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="809" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A809" s="10">
+        <v>46279</v>
+      </c>
+      <c r="E809">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="810" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A810" s="10">
+        <v>46297</v>
+      </c>
+      <c r="E810">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="811" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A811" s="10">
+        <v>46273</v>
+      </c>
+      <c r="E811">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="812" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A812" s="10">
+        <v>46282</v>
+      </c>
+      <c r="E812">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="813" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A813" s="10">
+        <v>46294</v>
+      </c>
+      <c r="E813">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="814" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A814" s="10">
+        <v>46300</v>
+      </c>
+      <c r="E814">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="815" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A815" s="10">
+        <v>46276</v>
+      </c>
+      <c r="E815">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="816" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A816" s="10">
+        <v>46288</v>
+      </c>
+      <c r="E816">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="817" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A817" s="10">
+        <v>46290</v>
+      </c>
+      <c r="E817">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="818" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A818" s="10">
+        <v>46302</v>
+      </c>
+      <c r="E818">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="819" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A819" s="10">
+        <v>46296</v>
+      </c>
+      <c r="E819">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="820" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A820" s="10">
+        <v>46286</v>
+      </c>
+      <c r="E820">
         <v>1</v>
       </c>
     </row>
@@ -9824,15 +10158,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <Confidentiality xmlns="ee2de805-d424-449f-84ad-9da0e2dd7d39">Intern</Confidentiality>
@@ -9843,6 +10168,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10063,26 +10397,26 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0DBF876-E745-42DF-BD17-181B14022097}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF03F65C-5CED-4A89-8A63-D9B2AEB56D23}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="ee2de805-d424-449f-84ad-9da0e2dd7d39"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="4c57b41f-cbf4-457f-bf80-bd53c8e26310"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF03F65C-5CED-4A89-8A63-D9B2AEB56D23}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0DBF876-E745-42DF-BD17-181B14022097}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="4c57b41f-cbf4-457f-bf80-bd53c8e26310"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="ee2de805-d424-449f-84ad-9da0e2dd7d39"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
